--- a/backend_api/templates/holds_inspection_certificate.xlsx
+++ b/backend_api/templates/holds_inspection_certificate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aaron Avila\Documents\ERP-SOM\backend_api\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1739CF6A-FA0B-476F-9796-E1B7C985CCB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0585E144-0DE8-4BCB-9B37-E29210813348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B5CF9ACD-A52E-4739-A569-C63BACEA7006}"/>
   </bookViews>
@@ -394,7 +394,7 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
@@ -402,15 +402,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -421,9 +419,9 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -431,15 +429,21 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -463,19 +467,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1010,25 +1001,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6658B9BE-1DBB-49BE-912F-793FC2E692DC}">
   <dimension ref="A1:J51"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9.88671875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="10.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="12.28515625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9.85546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="11" style="2" customWidth="1"/>
-    <col min="7" max="7" width="10.6640625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="24.6640625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="12.88671875" style="2" customWidth="1"/>
-    <col min="10" max="256" width="11.5546875" style="2" customWidth="1"/>
-    <col min="257" max="16384" width="8.88671875" style="2"/>
+    <col min="7" max="7" width="10.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="24.7109375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="12.85546875" style="2" customWidth="1"/>
+    <col min="10" max="256" width="11.5703125" style="2" customWidth="1"/>
+    <col min="257" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.25">
       <c r="I1" s="3"/>
     </row>
-    <row r="2" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="18" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1039,9 +1030,9 @@
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
     </row>
-    <row r="4" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="6" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="26" t="s">
         <v>4</v>
       </c>
@@ -1053,8 +1044,8 @@
       <c r="G6" s="26"/>
       <c r="H6" s="26"/>
     </row>
-    <row r="7" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>3</v>
       </c>
@@ -1062,138 +1053,114 @@
         <f>+data!B5</f>
         <v>0</v>
       </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="35">
+      <c r="H8" s="8">
         <f>+data!B6</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="4">
         <f>+data!B7</f>
         <v>0</v>
       </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="H9" s="25">
+      <c r="H9" s="22">
         <f>+data!B8</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="4">
         <f>+data!B9</f>
         <v>0</v>
       </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="H10" s="9"/>
-    </row>
-    <row r="11" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H10" s="7"/>
+    </row>
+    <row r="11" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="34">
+      <c r="C11" s="23">
         <f>+data!B11</f>
         <v>0</v>
       </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-    </row>
-    <row r="12" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="4">
         <f>+data!B10</f>
         <v>0</v>
       </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-    </row>
-    <row r="15" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="10" t="s">
+    </row>
+    <row r="15" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="23" t="s">
+    <row r="16" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="38">
+      <c r="E16" s="25">
         <f>+data!B12</f>
         <v>0</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
+    <row r="17" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A17" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
-    </row>
-    <row r="19" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+    </row>
+    <row r="19" spans="1:8" ht="18" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E19" s="37">
+      <c r="E19" s="33">
         <f>+data!B13</f>
         <v>0</v>
       </c>
-      <c r="F19" s="37"/>
-    </row>
-    <row r="21" spans="1:8" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
+      <c r="F19" s="33"/>
+    </row>
+    <row r="21" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A21" s="10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
+    <row r="22" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A22" s="10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A24" s="36">
+    <row r="24" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A24" s="24">
         <f>+data!B14</f>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A25" s="12"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-    </row>
-    <row r="27" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A25" s="10"/>
+    </row>
+    <row r="27" spans="1:8" ht="18" x14ac:dyDescent="0.25">
       <c r="A27" s="33" t="s">
         <v>24</v>
       </c>
@@ -1205,134 +1172,118 @@
       <c r="G27" s="33"/>
       <c r="H27" s="33"/>
     </row>
-    <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:8" ht="18" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D29" s="37">
+      <c r="D29" s="33">
         <f>+E19</f>
         <v>0</v>
       </c>
-      <c r="E29" s="37"/>
-      <c r="F29" s="37"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="24"/>
-    </row>
-    <row r="31" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="22" t="s">
+      <c r="E29" s="33"/>
+      <c r="F29" s="33"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="21"/>
+    </row>
+    <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="38">
+      <c r="C31" s="25">
         <f>+data!B16</f>
         <v>0</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="D31" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H31" s="6"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-    </row>
-    <row r="33" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="A33" s="13" t="s">
+    </row>
+    <row r="33" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+      <c r="A33" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B33" s="14">
+      <c r="B33" s="12">
         <f>H9</f>
         <v>0</v>
       </c>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
-    </row>
-    <row r="35" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="A35" s="13" t="s">
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+    </row>
+    <row r="35" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B35" s="16">
+      <c r="B35" s="14">
         <f>C11</f>
         <v>0</v>
       </c>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="J35" s="17"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J35" s="15"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="str">
         <f>CONCATENATE("Water Tightness / Hose Test time: ",data!B19," ","to", data!B20,"'VESSEL HOLDS INSPECTION CERTIFI'! ","hour´s local time")</f>
         <v>Water Tightness / Hose Test time:  to'VESSEL HOLDS INSPECTION CERTIFI'! hour´s local time</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B38" s="19"/>
-    </row>
-    <row r="40" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B38" s="17"/>
+    </row>
+    <row r="40" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B40" s="20"/>
-      <c r="C40" s="20"/>
-      <c r="D40" s="20"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="20"/>
-      <c r="G40" s="20"/>
-      <c r="H40" s="20"/>
-      <c r="I40" s="20"/>
-    </row>
-    <row r="41" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A41" s="18">
+      <c r="B40" s="18"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="18"/>
+    </row>
+    <row r="41" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="A41" s="16">
         <f>+data!B21</f>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A42" s="17"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="20" t="s">
+    <row r="42" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="A42" s="15"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A44" s="18" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="21" t="s">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A45" s="19" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A50" s="29" t="s">
         <v>18</v>
       </c>
       <c r="B50" s="30"/>
       <c r="C50" s="30"/>
-      <c r="D50" s="13"/>
-      <c r="E50" s="13"/>
-      <c r="G50" s="29"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
+      <c r="G50" s="29">
+        <f>+data!B25</f>
+        <v>0</v>
+      </c>
       <c r="H50" s="30"/>
     </row>
-    <row r="51" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="27" t="s">
         <v>0</v>
       </c>
       <c r="B51" s="28"/>
       <c r="C51" s="28"/>
-      <c r="D51" s="13"/>
-      <c r="E51" s="13"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
       <c r="G51" s="31" t="s">
         <v>26</v>
       </c>
@@ -1361,132 +1312,132 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0B9FB0B-4ACA-418C-8405-61D69C0DEE97}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>51</v>
       </c>

--- a/backend_api/templates/holds_inspection_certificate.xlsx
+++ b/backend_api/templates/holds_inspection_certificate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aaron Avila\Documents\ERP-SOM\backend_api\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0585E144-0DE8-4BCB-9B37-E29210813348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{656A7E01-E29E-44D0-BF41-C3AEA5A839CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B5CF9ACD-A52E-4739-A569-C63BACEA7006}"/>
   </bookViews>

--- a/backend_api/templates/holds_inspection_certificate.xlsx
+++ b/backend_api/templates/holds_inspection_certificate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aaron Avila\Documents\ERP-SOM\backend_api\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{656A7E01-E29E-44D0-BF41-C3AEA5A839CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42EA2A7D-5C99-44DD-B6AE-759351DD3D13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B5CF9ACD-A52E-4739-A569-C63BACEA7006}"/>
   </bookViews>
@@ -78,12 +78,6 @@
     <t>INSPECTION WERE FOUND TO BE:</t>
   </si>
   <si>
-    <t>IT MAY CONCERN.</t>
-  </si>
-  <si>
-    <t>THIS SURVEY  IS ISSUED WITHOUT PREJUDICE WITH THE BEST OF MY KNOWLEDGE AND ABILITY AND FOR BENEFIT OF WHOM</t>
-  </si>
-  <si>
     <t xml:space="preserve">VOYAGE #: </t>
   </si>
   <si>
@@ -105,21 +99,96 @@
     <t xml:space="preserve">ON BOARD THE SUBJECT VESSEL AT  </t>
   </si>
   <si>
+    <t>PLACE #:</t>
+  </si>
+  <si>
+    <t>YELLOW CORN IN BULK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSTALLATION: </t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>report_number</t>
+  </si>
+  <si>
+    <t>port</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>vessel</t>
+  </si>
+  <si>
+    <t>voyage</t>
+  </si>
+  <si>
+    <t>load_port</t>
+  </si>
+  <si>
+    <t>place</t>
+  </si>
+  <si>
+    <t>installation</t>
+  </si>
+  <si>
+    <t>product</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>inspection_time</t>
+  </si>
+  <si>
+    <t>vessel_holds</t>
+  </si>
+  <si>
+    <t>vessel_holds_status</t>
+  </si>
+  <si>
+    <t>cargo_holds</t>
+  </si>
+  <si>
+    <t>accepted_time</t>
+  </si>
+  <si>
+    <t>place_location</t>
+  </si>
+  <si>
+    <t>place_date</t>
+  </si>
+  <si>
+    <t>hose_test_start</t>
+  </si>
+  <si>
+    <t>hose_test_end</t>
+  </si>
+  <si>
+    <t>remarks</t>
+  </si>
+  <si>
+    <t>created_at</t>
+  </si>
+  <si>
+    <t>updated_at</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>master_chief_officer</t>
+  </si>
+  <si>
     <r>
-      <t>THIS REPORT IS TO CERTIFY</t>
+      <t>THIS REPORT IS TO CERTIFY,</t>
     </r>
     <r>
       <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+        <sz val="9"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -127,21 +196,12 @@
     </r>
   </si>
   <si>
-    <t>PLACE #:</t>
-  </si>
-  <si>
-    <t>YELLOW CORN IN BULK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INSTALLATION: </t>
-  </si>
-  <si>
     <r>
       <t>MASTER</t>
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="9"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -149,155 +209,20 @@
     </r>
   </si>
   <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>report_number</t>
-  </si>
-  <si>
-    <t>port</t>
-  </si>
-  <si>
-    <t>country</t>
-  </si>
-  <si>
-    <t>vessel</t>
-  </si>
-  <si>
-    <t>voyage</t>
-  </si>
-  <si>
-    <t>load_port</t>
-  </si>
-  <si>
-    <t>place</t>
-  </si>
-  <si>
-    <t>installation</t>
-  </si>
-  <si>
-    <t>product</t>
-  </si>
-  <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>inspection_time</t>
-  </si>
-  <si>
-    <t>vessel_holds</t>
-  </si>
-  <si>
-    <t>vessel_holds_status</t>
-  </si>
-  <si>
-    <t>cargo_holds</t>
-  </si>
-  <si>
-    <t>accepted_time</t>
-  </si>
-  <si>
-    <t>place_location</t>
-  </si>
-  <si>
-    <t>place_date</t>
-  </si>
-  <si>
-    <t>hose_test_start</t>
-  </si>
-  <si>
-    <t>hose_test_end</t>
-  </si>
-  <si>
-    <t>remarks</t>
-  </si>
-  <si>
-    <t>created_at</t>
-  </si>
-  <si>
-    <t>updated_at</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>master_chief_officer</t>
+    <t xml:space="preserve">THIS SURVEY  IS ISSUED WITHOUT PREJUDICE WITH THE BEST OF MY KNOWLEDGE AND ABILITY AND FOR BENEFIT </t>
+  </si>
+  <si>
+    <t>OF WHOM IT MAY CONCERN.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="14"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -319,9 +244,26 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
       <u/>
-      <sz val="13"/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -390,83 +332,54 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -578,15 +491,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>53340</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
+      <xdr:colOff>46013</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>56565</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>160020</xdr:rowOff>
+      <xdr:colOff>487973</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>13482</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -616,8 +529,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="53340" y="137160"/>
-          <a:ext cx="2674620" cy="845820"/>
+          <a:off x="46013" y="210430"/>
+          <a:ext cx="2610729" cy="704264"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1001,208 +914,205 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6658B9BE-1DBB-49BE-912F-793FC2E692DC}">
   <dimension ref="A1:J51"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="11" style="2" customWidth="1"/>
-    <col min="7" max="7" width="10.7109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="24.7109375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="12.85546875" style="2" customWidth="1"/>
-    <col min="10" max="256" width="11.5703125" style="2" customWidth="1"/>
-    <col min="257" max="16384" width="8.85546875" style="2"/>
+    <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="24.7109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.85546875" style="1" customWidth="1"/>
+    <col min="10" max="256" width="11.5703125" style="1" customWidth="1"/>
+    <col min="257" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.25">
-      <c r="I1" s="3"/>
-    </row>
-    <row r="2" spans="1:9" ht="18" x14ac:dyDescent="0.25">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I1" s="2"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
     </row>
     <row r="4" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="6" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="26" t="s">
+    <row r="6" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
     </row>
     <row r="7" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="4">
         <f>+data!B5</f>
         <v>0</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="6">
+        <f>+data!B6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1">
+        <f>+data!B7</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="6">
+        <f>+data!B8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1">
+        <f>+data!B9</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="7"/>
+    </row>
+    <row r="11" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="7">
+        <f>+data!B11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="1">
+        <f>+data!B10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="8">
+        <f>+data!B12</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="8">
-        <f>+data!B6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="4">
-        <f>+data!B7</f>
-        <v>0</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="22">
-        <f>+data!B8</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="4">
-        <f>+data!B9</f>
-        <v>0</v>
-      </c>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="23">
-        <f>+data!B11</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="4">
-        <f>+data!B10</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="20" t="s">
+      <c r="E19" s="11">
+        <f>+data!B13</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="11"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" s="12">
+        <f>+data!B14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="25">
-        <f>+data!B12</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A17" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-    </row>
-    <row r="19" spans="1:8" ht="18" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E19" s="33">
-        <f>+data!B13</f>
-        <v>0</v>
-      </c>
-      <c r="F19" s="33"/>
-    </row>
-    <row r="21" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A21" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A22" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A24" s="24">
-        <f>+data!B14</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A25" s="10"/>
-    </row>
-    <row r="27" spans="1:8" ht="18" x14ac:dyDescent="0.25">
-      <c r="A27" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27" s="33"/>
-      <c r="C27" s="33"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="33"/>
-      <c r="H27" s="33"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
     </row>
     <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:8" ht="18" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D29" s="33">
+      <c r="D29" s="11">
         <f>+E19</f>
         <v>0</v>
       </c>
-      <c r="E29" s="33"/>
-      <c r="F29" s="33"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="21"/>
-    </row>
-    <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="25">
+      <c r="C31" s="8">
         <f>+data!B16</f>
         <v>0</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="D31" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="15" x14ac:dyDescent="0.2">
-      <c r="A33" s="11" t="s">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B33" s="12">
+      <c r="B33" s="1">
         <f>H9</f>
         <v>0</v>
       </c>
@@ -1211,83 +1121,71 @@
       <c r="E33" s="13"/>
       <c r="F33" s="13"/>
     </row>
-    <row r="35" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="11" t="s">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B35" s="14">
         <f>C11</f>
         <v>0</v>
       </c>
-      <c r="J35" s="15"/>
+      <c r="J35" s="10"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B37" s="2" t="str">
+      <c r="B37" s="1" t="str">
         <f>CONCATENATE("Water Tightness / Hose Test time: ",data!B19," ","to", data!B20,"'VESSEL HOLDS INSPECTION CERTIFI'! ","hour´s local time")</f>
         <v>Water Tightness / Hose Test time:  to'VESSEL HOLDS INSPECTION CERTIFI'! hour´s local time</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B38" s="17"/>
-    </row>
-    <row r="40" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
+      <c r="B38" s="10"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A40" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A41" s="4">
+        <f>+data!B21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A42" s="10"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A44" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A50" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B40" s="18"/>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18"/>
-      <c r="G40" s="18"/>
-      <c r="H40" s="18"/>
-      <c r="I40" s="18"/>
-    </row>
-    <row r="41" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="A41" s="16">
-        <f>+data!B21</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="A42" s="15"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A44" s="18" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A45" s="19" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A50" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="B50" s="30"/>
-      <c r="C50" s="30"/>
-      <c r="D50" s="11"/>
-      <c r="E50" s="11"/>
-      <c r="G50" s="29">
+      <c r="B50" s="15"/>
+      <c r="C50" s="15"/>
+      <c r="G50" s="15">
         <f>+data!B25</f>
         <v>0</v>
       </c>
-      <c r="H50" s="30"/>
-    </row>
-    <row r="51" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="B51" s="28"/>
-      <c r="C51" s="28"/>
-      <c r="D51" s="11"/>
-      <c r="E51" s="11"/>
-      <c r="G51" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="H51" s="32"/>
+      <c r="H50" s="15"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A51" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B51" s="16"/>
+      <c r="C51" s="16"/>
+      <c r="G51" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="H51" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1302,7 +1200,7 @@
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.47" right="0.25" top="0.3" bottom="0.53" header="0.27" footer="0.5"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="146" orientation="portrait" horizontalDpi="150" verticalDpi="150" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId2"/>
@@ -1319,127 +1217,127 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/backend_api/templates/holds_inspection_certificate.xlsx
+++ b/backend_api/templates/holds_inspection_certificate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aaron Avila\Documents\ERP-SOM\backend_api\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42EA2A7D-5C99-44DD-B6AE-759351DD3D13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACE3A1BC-BC5A-405D-B63A-BD81936ED1FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B5CF9ACD-A52E-4739-A569-C63BACEA7006}"/>
   </bookViews>
@@ -342,9 +342,6 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -364,22 +361,25 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -921,7 +921,7 @@
     <col min="3" max="3" width="10.28515625" style="1" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="10.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" style="1" customWidth="1"/>
     <col min="7" max="7" width="10.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="24.7109375" style="1" customWidth="1"/>
     <col min="9" max="9" width="12.85546875" style="1" customWidth="1"/>
@@ -946,30 +946,30 @@
     <row r="4" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="6" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
     </row>
     <row r="7" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="3">
         <f>+data!B5</f>
         <v>0</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="F8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="6">
+      <c r="G8" s="5">
         <f>+data!B6</f>
         <v>0</v>
       </c>
@@ -982,10 +982,10 @@
         <f>+data!B7</f>
         <v>0</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="F9" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="6">
+      <c r="G9" s="5">
         <f>+data!B8</f>
         <v>0</v>
       </c>
@@ -998,13 +998,13 @@
         <f>+data!B9</f>
         <v>0</v>
       </c>
-      <c r="H10" s="7"/>
+      <c r="H10" s="6"/>
     </row>
     <row r="11" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="6">
         <f>+data!B11</f>
         <v>0</v>
       </c>
@@ -1019,19 +1019,19 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="5" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="7">
         <f>+data!B12</f>
         <v>0</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="8" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1041,18 +1041,18 @@
       </c>
     </row>
     <row r="18" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="18">
         <f>+data!B13</f>
         <v>0</v>
       </c>
-      <c r="F19" s="11"/>
+      <c r="F19" s="18"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
@@ -1065,42 +1065,42 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="12">
+      <c r="A24" s="10">
         <f>+data!B14</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
     </row>
     <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="10" t="s">
+      <c r="A29" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="18">
         <f>+E19</f>
         <v>0</v>
       </c>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="8">
+      <c r="C31" s="7">
         <f>+data!B16</f>
         <v>0</v>
       </c>
@@ -1113,23 +1113,23 @@
         <v>1</v>
       </c>
       <c r="B33" s="1">
-        <f>H9</f>
-        <v>0</v>
-      </c>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
+        <f>G9</f>
+        <v>0</v>
+      </c>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B35" s="14">
+      <c r="B35" s="12">
         <f>C11</f>
         <v>0</v>
       </c>
-      <c r="J35" s="10"/>
+      <c r="J35" s="9"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="str">
@@ -1138,21 +1138,21 @@
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B38" s="10"/>
+      <c r="B38" s="9"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A40" s="10" t="s">
+      <c r="A40" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A41" s="4">
+      <c r="A41" s="3">
         <f>+data!B21</f>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A42" s="10"/>
+      <c r="A42" s="9"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -1164,36 +1164,36 @@
         <v>51</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="15" t="s">
         <v>16</v>
       </c>
       <c r="B50" s="15"/>
       <c r="C50" s="15"/>
-      <c r="G50" s="15">
+      <c r="E50" s="15">
         <f>+data!B25</f>
         <v>0</v>
       </c>
-      <c r="H50" s="15"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A51" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B51" s="16"/>
-      <c r="C51" s="16"/>
-      <c r="G51" s="17" t="s">
+      <c r="F50" s="15"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A51" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B51" s="14"/>
+      <c r="C51" s="14"/>
+      <c r="E51" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="H51" s="18"/>
+      <c r="F51" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A6:H6"/>
     <mergeCell ref="A51:C51"/>
     <mergeCell ref="A50:C50"/>
-    <mergeCell ref="G50:H50"/>
-    <mergeCell ref="G51:H51"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="E51:F51"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="D29:F29"/>
